--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:21:18+00:00</t>
+    <t>2025-02-10T11:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2638" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2565" uniqueCount="483">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:27:45+00:00</t>
+    <t>2025-02-12T10:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -431,21 +431,21 @@
     <t>Encounter.extension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -455,53 +455,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Encounter.extension:PhysischeAnwesenheit</t>
-  </si>
-  <si>
-    <t>PhysischeAnwesenheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-physischeAnwesenheit}
-</t>
-  </si>
-  <si>
-    <t>physische Anwesenheit</t>
-  </si>
-  <si>
-    <t>Ob der Patient physisch anwesend war.</t>
-  </si>
-  <si>
-    <t>Encounter.extension:Altersgruppe</t>
-  </si>
-  <si>
-    <t>Altersgruppe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-Altersgruppe}
-</t>
-  </si>
-  <si>
-    <t>In Gruppen eingeteilt, wobei vollendete Lebensjahre ausschlaggebend sind.</t>
-  </si>
-  <si>
-    <t>Encounter.extension:Neugeborenes</t>
-  </si>
-  <si>
-    <t>Neugeborenes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-Neugeborenes}
-</t>
-  </si>
-  <si>
-    <t>Ein Patient wird als Neugeborenes bezeichnet, wenn das Alter zum Zugangszeitpunkt auf die Abteilung &lt;28 Tage ist.</t>
-  </si>
-  <si>
     <t>Encounter.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
   </si>
   <si>
     <t>Extensions that cannot be ignored</t>
@@ -511,9 +465,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -729,10 +680,7 @@
     <t>Different use-cases are likely to have different permitted transitions between states, such as an Emergency department could use `arrived` when the patient first presents, then `triaged` once has been assessed by a nurse, then `receiving-care` once treatment begins, however other sectors may use a different set of these values, or their own custom set in place of this example valueset provided.</t>
   </si>
   <si>
-    <t>Current status of the subject  within the encounter.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-subject-status</t>
+    <t>http://example.org/ValueSet/moped-Anwesenheitsart-valueset</t>
   </si>
   <si>
     <t>Encounter.episodeOfCare</t>
@@ -886,9 +834,6 @@
   </si>
   <si>
     <t>Encounter.participant.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -1373,6 +1318,36 @@
   </si>
   <si>
     <t>Encounter.admission.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Encounter.admission.extension:Altersgruppe</t>
+  </si>
+  <si>
+    <t>Altersgruppe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-altersgruppe}
+</t>
+  </si>
+  <si>
+    <t>In Gruppen eingeteilt, wobei vollendete Lebensjahre ausschlaggebend sind.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}moped-inv-Altersgruppe-1:If 'neugeborenes' is true then 'beiZugang' must be age group 0. {$this.extension('neugeborenes') = true implies $this.extension('beiZugang') = '0'}</t>
   </si>
   <si>
     <t>Encounter.admission.modifierExtension</t>
@@ -1870,12 +1845,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN73"/>
+  <dimension ref="A1:AN71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="41.58984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.3125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="41.58984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="21.921875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.8984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1898,7 +1873,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="74.65625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.25390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.48046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -2839,7 +2814,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2858,15 +2833,17 @@
         <v>19</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>19</v>
@@ -2903,14 +2880,16 @@
         <v>19</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>139</v>
@@ -2934,7 +2913,7 @@
         <v>19</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>19</v>
@@ -2945,41 +2924,43 @@
         <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>19</v>
       </c>
@@ -3027,7 +3008,7 @@
         <v>19</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -3048,7 +3029,7 @@
         <v>19</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>19</v>
@@ -3059,11 +3040,9 @@
         <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>19</v>
       </c>
@@ -3072,7 +3051,7 @@
         <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>19</v>
@@ -3081,13 +3060,13 @@
         <v>19</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
         <v>149</v>
@@ -3141,7 +3120,7 @@
         <v>19</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -3153,37 +3132,35 @@
         <v>19</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>19</v>
+        <v>151</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>19</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>87</v>
@@ -3192,21 +3169,23 @@
         <v>19</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>152</v>
+        <v>107</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>19</v>
@@ -3231,13 +3210,13 @@
         <v>19</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>19</v>
@@ -3255,43 +3234,43 @@
         <v>19</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>19</v>
+        <v>160</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>19</v>
+        <v>162</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>19</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3304,26 +3283,22 @@
         <v>19</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>19</v>
       </c>
@@ -3347,13 +3322,13 @@
         <v>19</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>19</v>
@@ -3371,7 +3346,7 @@
         <v>19</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3383,27 +3358,27 @@
         <v>19</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>19</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3414,7 +3389,7 @@
         <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>19</v>
@@ -3423,16 +3398,16 @@
         <v>19</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3459,13 +3434,13 @@
         <v>19</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>19</v>
+        <v>176</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>19</v>
+        <v>178</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>19</v>
@@ -3483,13 +3458,13 @@
         <v>19</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>19</v>
@@ -3498,24 +3473,24 @@
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>165</v>
+        <v>19</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>168</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3523,31 +3498,31 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>107</v>
+        <v>165</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3573,13 +3548,13 @@
         <v>19</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>111</v>
+        <v>177</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>19</v>
@@ -3597,13 +3572,13 @@
         <v>19</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>19</v>
@@ -3612,24 +3587,24 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>178</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3652,13 +3627,13 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3685,13 +3660,13 @@
         <v>19</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>19</v>
@@ -3709,7 +3684,7 @@
         <v>19</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3724,28 +3699,28 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>19</v>
+        <v>188</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>186</v>
+        <v>19</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>188</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>19</v>
+        <v>201</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3761,18 +3736,20 @@
         <v>19</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>19</v>
@@ -3797,13 +3774,13 @@
         <v>19</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>192</v>
+        <v>19</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>191</v>
+        <v>19</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>193</v>
+        <v>19</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>19</v>
@@ -3821,7 +3798,7 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3836,24 +3813,24 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>19</v>
+        <v>206</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>196</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3864,7 +3841,7 @@
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>19</v>
@@ -3873,19 +3850,19 @@
         <v>19</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3911,13 +3888,11 @@
         <v>19</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>19</v>
@@ -3935,13 +3910,13 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>19</v>
@@ -3950,24 +3925,24 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>203</v>
+        <v>19</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>204</v>
+        <v>19</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>205</v>
+        <v>19</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>206</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3990,13 +3965,13 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4023,13 +3998,13 @@
         <v>19</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>192</v>
+        <v>19</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>211</v>
+        <v>19</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>212</v>
+        <v>19</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>19</v>
@@ -4047,7 +4022,7 @@
         <v>19</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -4062,35 +4037,35 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>203</v>
+        <v>19</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>19</v>
+        <v>219</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>19</v>
@@ -4099,20 +4074,18 @@
         <v>19</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>19</v>
@@ -4161,13 +4134,13 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>19</v>
@@ -4176,24 +4149,24 @@
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>222</v>
+        <v>19</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>224</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4204,7 +4177,7 @@
         <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>19</v>
@@ -4216,17 +4189,15 @@
         <v>19</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>180</v>
+        <v>229</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>19</v>
@@ -4251,13 +4222,13 @@
         <v>19</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>192</v>
+        <v>19</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>229</v>
+        <v>19</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>230</v>
+        <v>19</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>19</v>
@@ -4275,13 +4246,13 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>19</v>
@@ -4296,7 +4267,7 @@
         <v>19</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>19</v>
+        <v>198</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>19</v>
@@ -4304,10 +4275,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4318,7 +4289,7 @@
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>19</v>
@@ -4327,18 +4298,20 @@
         <v>19</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>19</v>
@@ -4387,13 +4360,13 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>19</v>
@@ -4402,35 +4375,35 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>19</v>
+        <v>237</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>235</v>
+        <v>19</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>236</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>238</v>
+        <v>19</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>19</v>
@@ -4442,13 +4415,13 @@
         <v>19</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4499,13 +4472,13 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>19</v>
@@ -4514,24 +4487,24 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>19</v>
+        <v>245</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4551,18 +4524,20 @@
         <v>19</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>19</v>
@@ -4611,7 +4586,7 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4623,27 +4598,27 @@
         <v>19</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>251</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>19</v>
+        <v>252</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>19</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4666,17 +4641,15 @@
         <v>19</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>19</v>
@@ -4725,7 +4698,7 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4734,19 +4707,19 @@
         <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>253</v>
+        <v>19</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>254</v>
+        <v>198</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>19</v>
@@ -4754,21 +4727,21 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>19</v>
@@ -4780,15 +4753,17 @@
         <v>19</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>256</v>
+        <v>135</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>257</v>
+        <v>136</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>19</v>
@@ -4837,43 +4812,43 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>259</v>
+        <v>19</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>260</v>
+        <v>198</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>261</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>19</v>
+        <v>265</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4886,24 +4861,26 @@
         <v>19</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>263</v>
+        <v>135</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>19</v>
       </c>
@@ -4951,7 +4928,7 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4963,27 +4940,27 @@
         <v>19</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>267</v>
+        <v>140</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>268</v>
+        <v>19</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>269</v>
+        <v>132</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>270</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4994,7 +4971,7 @@
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>19</v>
@@ -5003,18 +4980,20 @@
         <v>19</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L28" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>19</v>
@@ -5039,13 +5018,13 @@
         <v>19</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>19</v>
+        <v>273</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>19</v>
+        <v>271</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>19</v>
+        <v>274</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>19</v>
@@ -5063,50 +5042,50 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI28" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AG28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI28" t="s" s="2">
+      <c r="AJ28" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>19</v>
-      </c>
       <c r="AL28" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>213</v>
+        <v>277</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>19</v>
+        <v>278</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>19</v>
@@ -5118,17 +5097,15 @@
         <v>19</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>134</v>
+        <v>280</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>19</v>
@@ -5177,19 +5154,19 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>19</v>
@@ -5198,54 +5175,52 @@
         <v>19</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>213</v>
+        <v>283</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>19</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>282</v>
+        <v>19</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>134</v>
+        <v>286</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>19</v>
       </c>
@@ -5299,33 +5274,33 @@
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>19</v>
+        <v>275</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>19</v>
+        <v>243</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>19</v>
+        <v>290</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>132</v>
+        <v>291</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>19</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5348,17 +5323,15 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>180</v>
+        <v>294</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>19</v>
@@ -5383,13 +5356,13 @@
         <v>19</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>290</v>
+        <v>19</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>288</v>
+        <v>19</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>291</v>
+        <v>19</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>19</v>
@@ -5407,7 +5380,7 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5416,30 +5389,30 @@
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>292</v>
+        <v>19</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>293</v>
+        <v>226</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5450,7 +5423,7 @@
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>19</v>
@@ -5462,15 +5435,17 @@
         <v>19</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>19</v>
@@ -5519,13 +5494,13 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>19</v>
@@ -5540,18 +5515,18 @@
         <v>19</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>300</v>
+        <v>132</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>301</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5571,19 +5546,19 @@
         <v>19</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5633,7 +5608,7 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5642,30 +5617,30 @@
         <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>292</v>
+        <v>19</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>259</v>
+        <v>308</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5676,7 +5651,7 @@
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>19</v>
@@ -5685,16 +5660,16 @@
         <v>19</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5745,13 +5720,13 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>19</v>
@@ -5760,24 +5735,24 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>242</v>
+        <v>19</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>314</v>
+        <v>19</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5788,7 +5763,7 @@
         <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>19</v>
@@ -5800,7 +5775,7 @@
         <v>19</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>318</v>
@@ -5808,9 +5783,7 @@
       <c r="M35" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N35" t="s" s="2">
-        <v>320</v>
-      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>19</v>
@@ -5859,13 +5832,13 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>19</v>
@@ -5880,10 +5853,10 @@
         <v>19</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>19</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36">
@@ -5914,16 +5887,16 @@
         <v>19</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5988,24 +5961,24 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>328</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6016,7 +5989,7 @@
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>19</v>
@@ -6025,18 +5998,20 @@
         <v>19</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>19</v>
@@ -6085,13 +6060,13 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>19</v>
@@ -6109,15 +6084,15 @@
         <v>19</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>333</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6140,13 +6115,13 @@
         <v>19</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>330</v>
+        <v>256</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>335</v>
+        <v>257</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>336</v>
+        <v>258</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6197,7 +6172,7 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>334</v>
+        <v>259</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6206,10 +6181,10 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>19</v>
@@ -6218,29 +6193,29 @@
         <v>19</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>19</v>
+        <v>198</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>337</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>19</v>
@@ -6252,16 +6227,16 @@
         <v>19</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>339</v>
+        <v>135</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>340</v>
+        <v>136</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>341</v>
+        <v>262</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>342</v>
+        <v>138</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6311,43 +6286,43 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>338</v>
+        <v>263</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>325</v>
+        <v>19</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>343</v>
+        <v>198</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>344</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>19</v>
+        <v>265</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6360,24 +6335,26 @@
         <v>19</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>263</v>
+        <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>346</v>
+        <v>266</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>347</v>
+        <v>267</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>19</v>
       </c>
@@ -6425,7 +6402,7 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>345</v>
+        <v>268</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6437,7 +6414,7 @@
         <v>19</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>19</v>
@@ -6446,7 +6423,7 @@
         <v>19</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>19</v>
@@ -6454,10 +6431,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6468,7 +6445,7 @@
         <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>19</v>
@@ -6477,16 +6454,16 @@
         <v>19</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>272</v>
+        <v>165</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>273</v>
+        <v>336</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>274</v>
+        <v>337</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6513,13 +6490,11 @@
         <v>19</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>19</v>
+        <v>338</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>19</v>
@@ -6537,19 +6512,19 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>275</v>
+        <v>335</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>19</v>
@@ -6558,7 +6533,7 @@
         <v>19</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>213</v>
+        <v>19</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>19</v>
@@ -6566,14 +6541,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>155</v>
+        <v>340</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6589,20 +6564,18 @@
         <v>19</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>134</v>
+        <v>341</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>278</v>
+        <v>342</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>19</v>
@@ -6627,13 +6600,13 @@
         <v>19</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>19</v>
+        <v>344</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>19</v>
+        <v>345</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>19</v>
@@ -6651,7 +6624,7 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>280</v>
+        <v>339</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6663,31 +6636,31 @@
         <v>19</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>19</v>
+        <v>346</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>19</v>
+        <v>347</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>213</v>
+        <v>348</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>19</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>282</v>
+        <v>19</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6700,26 +6673,24 @@
         <v>19</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>134</v>
+        <v>247</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>283</v>
+        <v>351</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>284</v>
+        <v>352</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>19</v>
       </c>
@@ -6767,7 +6738,7 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>285</v>
+        <v>350</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6779,7 +6750,7 @@
         <v>19</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>19</v>
@@ -6788,7 +6759,7 @@
         <v>19</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>132</v>
+        <v>354</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>19</v>
@@ -6796,10 +6767,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6810,7 +6781,7 @@
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>19</v>
@@ -6819,16 +6790,16 @@
         <v>19</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>180</v>
+        <v>256</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>353</v>
+        <v>257</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>354</v>
+        <v>258</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6855,11 +6826,13 @@
         <v>19</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>355</v>
+        <v>19</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>19</v>
@@ -6877,19 +6850,19 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>352</v>
+        <v>259</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>19</v>
@@ -6898,7 +6871,7 @@
         <v>19</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>19</v>
+        <v>198</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>19</v>
@@ -6913,7 +6886,7 @@
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>357</v>
+        <v>134</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6929,18 +6902,20 @@
         <v>19</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>358</v>
+        <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>359</v>
+        <v>136</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>19</v>
@@ -6965,13 +6940,13 @@
         <v>19</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>361</v>
+        <v>19</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>362</v>
+        <v>19</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>19</v>
@@ -6989,7 +6964,7 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>356</v>
+        <v>263</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -7001,31 +6976,31 @@
         <v>19</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>363</v>
+        <v>19</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>364</v>
+        <v>19</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>365</v>
+        <v>198</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>366</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>19</v>
+        <v>265</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7038,24 +7013,26 @@
         <v>19</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>263</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>368</v>
+        <v>266</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>369</v>
+        <v>267</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>19</v>
       </c>
@@ -7103,7 +7080,7 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>367</v>
+        <v>268</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7115,7 +7092,7 @@
         <v>19</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>19</v>
@@ -7124,7 +7101,7 @@
         <v>19</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>371</v>
+        <v>132</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>19</v>
@@ -7132,21 +7109,21 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>19</v>
+        <v>359</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>19</v>
@@ -7155,16 +7132,16 @@
         <v>19</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>272</v>
+        <v>360</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>273</v>
+        <v>361</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>274</v>
+        <v>362</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7191,13 +7168,11 @@
         <v>19</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>19</v>
+        <v>363</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>19</v>
@@ -7215,43 +7190,43 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>275</v>
+        <v>358</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>19</v>
+        <v>346</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>19</v>
+        <v>347</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>213</v>
+        <v>364</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>19</v>
+        <v>365</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7270,17 +7245,15 @@
         <v>19</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>278</v>
+        <v>367</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>19</v>
@@ -7305,13 +7278,13 @@
         <v>19</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>19</v>
+        <v>369</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>19</v>
+        <v>370</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>19</v>
@@ -7329,7 +7302,7 @@
         <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>280</v>
+        <v>366</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7341,7 +7314,7 @@
         <v>19</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>19</v>
@@ -7350,22 +7323,22 @@
         <v>19</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>19</v>
+        <v>371</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>282</v>
+        <v>19</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7378,26 +7351,24 @@
         <v>19</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>134</v>
+        <v>373</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>283</v>
+        <v>374</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>284</v>
+        <v>375</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>19</v>
       </c>
@@ -7445,7 +7416,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>285</v>
+        <v>372</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7457,7 +7428,7 @@
         <v>19</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>19</v>
@@ -7466,7 +7437,7 @@
         <v>19</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>132</v>
+        <v>377</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>19</v>
@@ -7474,14 +7445,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>376</v>
+        <v>19</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7497,19 +7468,23 @@
         <v>19</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>377</v>
+        <v>165</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>19</v>
       </c>
@@ -7533,11 +7508,13 @@
         <v>19</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>19</v>
@@ -7555,7 +7532,7 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7570,24 +7547,24 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>363</v>
+        <v>19</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>364</v>
+        <v>19</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7610,13 +7587,13 @@
         <v>19</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7643,31 +7620,31 @@
         <v>19</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="Z51" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7688,18 +7665,18 @@
         <v>19</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>213</v>
+        <v>392</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7722,16 +7699,16 @@
         <v>19</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>390</v>
+        <v>165</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7757,13 +7734,13 @@
         <v>19</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>19</v>
+        <v>398</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>19</v>
+        <v>399</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>19</v>
@@ -7781,7 +7758,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7802,18 +7779,18 @@
         <v>19</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>19</v>
+        <v>401</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7824,7 +7801,7 @@
         <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>19</v>
@@ -7836,20 +7813,18 @@
         <v>19</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>19</v>
       </c>
@@ -7873,13 +7848,13 @@
         <v>19</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>192</v>
+        <v>19</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>400</v>
+        <v>19</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>401</v>
+        <v>19</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>19</v>
@@ -7897,13 +7872,13 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>19</v>
@@ -7918,18 +7893,18 @@
         <v>19</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>403</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7940,7 +7915,7 @@
         <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>19</v>
@@ -7952,13 +7927,13 @@
         <v>19</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>180</v>
+        <v>256</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>405</v>
+        <v>257</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>406</v>
+        <v>258</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7985,13 +7960,13 @@
         <v>19</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>407</v>
+        <v>19</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>408</v>
+        <v>19</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>19</v>
@@ -8009,19 +7984,19 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>404</v>
+        <v>259</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>19</v>
@@ -8030,18 +8005,18 @@
         <v>19</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>409</v>
+        <v>198</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>410</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8064,17 +8039,15 @@
         <v>19</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>414</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>19</v>
@@ -8099,31 +8072,29 @@
         <v>19</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>415</v>
+        <v>19</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>416</v>
+        <v>19</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>19</v>
+        <v>412</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>411</v>
+        <v>263</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8135,7 +8106,7 @@
         <v>19</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>19</v>
@@ -8144,20 +8115,22 @@
         <v>19</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>417</v>
+        <v>19</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>418</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="C56" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="D56" t="s" s="2">
         <v>19</v>
       </c>
@@ -8178,17 +8151,15 @@
         <v>19</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>263</v>
+        <v>415</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>19</v>
@@ -8237,19 +8208,19 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>419</v>
+        <v>263</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>417</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>19</v>
@@ -8258,7 +8229,7 @@
         <v>19</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>423</v>
+        <v>19</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>19</v>
@@ -8266,42 +8237,46 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>19</v>
+        <v>265</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>272</v>
+        <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>19</v>
       </c>
@@ -8349,19 +8324,19 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>19</v>
@@ -8370,7 +8345,7 @@
         <v>19</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>213</v>
+        <v>132</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>19</v>
@@ -8378,21 +8353,21 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>19</v>
@@ -8404,17 +8379,15 @@
         <v>19</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>278</v>
+        <v>420</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>19</v>
@@ -8463,19 +8436,19 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>280</v>
+        <v>419</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>19</v>
@@ -8484,54 +8457,50 @@
         <v>19</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>213</v>
+        <v>152</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>19</v>
+        <v>422</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>282</v>
+        <v>19</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>134</v>
+        <v>424</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>283</v>
+        <v>425</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>19</v>
       </c>
@@ -8579,19 +8548,19 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>285</v>
+        <v>423</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>19</v>
@@ -8600,7 +8569,7 @@
         <v>19</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>132</v>
+        <v>427</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>19</v>
@@ -8608,10 +8577,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8634,13 +8603,13 @@
         <v>19</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8667,13 +8636,13 @@
         <v>19</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>19</v>
+        <v>431</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>19</v>
+        <v>432</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>19</v>
@@ -8691,7 +8660,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8712,18 +8681,18 @@
         <v>19</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>167</v>
+        <v>433</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8746,13 +8715,13 @@
         <v>19</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>432</v>
+        <v>165</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8779,13 +8748,13 @@
         <v>19</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>19</v>
+        <v>438</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>19</v>
+        <v>439</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>19</v>
@@ -8803,7 +8772,7 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8824,18 +8793,18 @@
         <v>19</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>435</v>
+        <v>198</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>19</v>
+        <v>440</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8858,13 +8827,13 @@
         <v>19</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>180</v>
+        <v>424</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8891,13 +8860,13 @@
         <v>19</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>439</v>
+        <v>19</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>440</v>
+        <v>19</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>19</v>
@@ -8915,7 +8884,7 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8936,18 +8905,18 @@
         <v>19</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8970,13 +8939,13 @@
         <v>19</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9003,31 +8972,29 @@
         <v>19</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y63" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y63" s="2"/>
+      <c r="Z63" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9048,18 +9015,18 @@
         <v>19</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>213</v>
+        <v>450</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9070,7 +9037,7 @@
         <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>19</v>
@@ -9082,15 +9049,17 @@
         <v>19</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>432</v>
+        <v>247</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>19</v>
@@ -9139,13 +9108,13 @@
         <v>19</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>19</v>
@@ -9160,18 +9129,18 @@
         <v>19</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>453</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9194,13 +9163,13 @@
         <v>19</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>180</v>
+        <v>256</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>455</v>
+        <v>257</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>456</v>
+        <v>258</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9227,11 +9196,13 @@
         <v>19</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="Y65" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z65" t="s" s="2">
-        <v>457</v>
+        <v>19</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>19</v>
@@ -9249,7 +9220,7 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>454</v>
+        <v>259</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9258,10 +9229,10 @@
         <v>87</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>19</v>
@@ -9270,22 +9241,22 @@
         <v>19</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>458</v>
+        <v>198</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>459</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9304,16 +9275,16 @@
         <v>19</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>263</v>
+        <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>461</v>
+        <v>136</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>462</v>
+        <v>262</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>463</v>
+        <v>138</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9363,7 +9334,7 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>460</v>
+        <v>263</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9375,7 +9346,7 @@
         <v>19</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>19</v>
@@ -9384,7 +9355,7 @@
         <v>19</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>464</v>
+        <v>198</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>19</v>
@@ -9392,42 +9363,46 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>19</v>
+        <v>265</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>272</v>
+        <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>19</v>
       </c>
@@ -9475,19 +9450,19 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>19</v>
@@ -9496,7 +9471,7 @@
         <v>19</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>213</v>
+        <v>132</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>19</v>
@@ -9504,21 +9479,21 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>19</v>
@@ -9530,17 +9505,15 @@
         <v>19</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>134</v>
+        <v>461</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>278</v>
+        <v>462</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>19</v>
@@ -9589,31 +9562,31 @@
         <v>19</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>280</v>
+        <v>460</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>19</v>
+        <v>464</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>19</v>
+        <v>465</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>213</v>
+        <v>291</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>19</v>
+        <v>466</v>
       </c>
     </row>
     <row r="69">
@@ -9625,39 +9598,37 @@
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>282</v>
+        <v>19</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>283</v>
+        <v>468</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>284</v>
+        <v>469</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>19</v>
       </c>
@@ -9681,13 +9652,13 @@
         <v>19</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>19</v>
+        <v>471</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>19</v>
+        <v>472</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>19</v>
@@ -9705,19 +9676,19 @@
         <v>19</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>285</v>
+        <v>467</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>19</v>
@@ -9726,7 +9697,7 @@
         <v>19</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>132</v>
+        <v>473</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>19</v>
@@ -9734,10 +9705,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9745,7 +9716,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>87</v>
@@ -9760,15 +9731,17 @@
         <v>19</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>469</v>
+        <v>165</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>476</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>19</v>
@@ -9793,13 +9766,13 @@
         <v>19</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>19</v>
+        <v>478</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>19</v>
+        <v>479</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>19</v>
@@ -9817,10 +9790,10 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>87</v>
@@ -9832,24 +9805,24 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>472</v>
+        <v>19</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>473</v>
+        <v>19</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>308</v>
+        <v>19</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>474</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9872,17 +9845,15 @@
         <v>19</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>107</v>
+        <v>280</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>19</v>
@@ -9907,31 +9878,31 @@
         <v>19</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>479</v>
+        <v>19</v>
       </c>
       <c r="Z71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9952,235 +9923,9 @@
         <v>19</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>481</v>
+        <v>283</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AN73" t="s" s="2">
         <v>19</v>
       </c>
     </row>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:32:14+00:00</t>
+    <t>2025-02-12T10:54:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:54:19+00:00</t>
+    <t>2025-02-13T11:55:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T11:55:14+00:00</t>
+    <t>2025-02-13T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:01:49+00:00</t>
+    <t>2025-02-13T12:22:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:22:49+00:00</t>
+    <t>2025-02-13T12:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/MopedTransferEncounter</t>
+    <t>https://elga.moped.at/StructureDefinition/MopedTransferEncounter</t>
   </si>
   <si>
     <t>Version</t>
@@ -54,19 +54,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:31:02+00:00</t>
+    <t>2025-02-13T14:17:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -680,7 +680,7 @@
     <t>Different use-cases are likely to have different permitted transitions between states, such as an Emergency department could use `arrived` when the patient first presents, then `triaged` once has been assessed by a nurse, then `receiving-care` once treatment begins, however other sectors may use a different set of these values, or their own custom set in place of this example valueset provided.</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-Anwesenheitsart-valueset</t>
+    <t>https://elga.moped.at/ValueSet/moped-Anwesenheitsart-valueset</t>
   </si>
   <si>
     <t>Encounter.episodeOfCare</t>
@@ -741,7 +741,7 @@
     <t>Encounter.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedEncounter)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedEncounter)
 </t>
   </si>
   <si>
@@ -765,7 +765,7 @@
     <t>Encounter.serviceProvider</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedOrganizationAbteilung)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedOrganizationAbteilung)
 </t>
   </si>
   <si>
@@ -1339,7 +1339,7 @@
     <t>Altersgruppe</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-altersgruppe}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-altersgruppe}
 </t>
   </si>
   <si>
@@ -1444,7 +1444,7 @@
     <t>Category or kind of location after discharge.</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-abgangsart-valueset</t>
+    <t>https://elga.moped.at/ValueSet/moped-abgangsart-valueset</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>
@@ -1873,7 +1873,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="74.65625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.48046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.1875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:17:28+00:00</t>
+    <t>2025-02-13T14:29:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:29:22+00:00</t>
+    <t>2025-02-13T14:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:40:19+00:00</t>
+    <t>2025-02-13T14:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:46:33+00:00</t>
+    <t>2025-02-13T14:59:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:59:23+00:00</t>
+    <t>2025-02-14T09:24:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:24:21+00:00</t>
+    <t>2025-02-14T09:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:29:02+00:00</t>
+    <t>2025-02-14T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:34:15+00:00</t>
+    <t>2025-02-19T07:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T07:14:32+00:00</t>
+    <t>2025-02-19T08:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T08:04:21+00:00</t>
+    <t>2025-02-19T15:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:11:41+00:00</t>
+    <t>2025-02-19T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:18:38+00:00</t>
+    <t>2025-02-19T15:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:13:59+00:00</t>
+    <t>2025-02-20T20:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:24:20+00:00</t>
+    <t>2025-02-27T10:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:01:21+00:00</t>
+    <t>2025-02-27T10:07:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:07:48+00:00</t>
+    <t>2025-03-01T14:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:47:03+00:00</t>
+    <t>2025-03-01T14:53:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:53:36+00:00</t>
+    <t>2025-03-01T15:19:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T15:19:11+00:00</t>
+    <t>2025-03-02T20:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:51:11+00:00</t>
+    <t>2025-03-02T20:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:57:05+00:00</t>
+    <t>2025-03-11T16:13:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:13:30+00:00</t>
+    <t>2025-03-11T16:22:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:22:04+00:00</t>
+    <t>2025-03-12T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedTransferEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T12:46:26+00:00</t>
+    <t>2025-03-12T14:39:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
